--- a/simulations/PARETO/Résultat avec contrainte/CO2_EQ.xlsx
+++ b/simulations/PARETO/Résultat avec contrainte/CO2_EQ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\PARETO\Résultat avec contrainte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AF1CF1-E791-486B-BC6B-65258956C329}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5989BC22-771F-4EFD-947A-7D4AACD15651}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results" sheetId="1" r:id="rId1"/>
